--- a/ComcastCRMGUIFramework/testdata/TestData.xlsx
+++ b/ComcastCRMGUIFramework/testdata/TestData.xlsx
@@ -3,9 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E5825A9E-935E-4B42-BBF0-F249F6E97BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Automation_TL\ComcastCRMGUIFramework\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC94EC7-9DB9-48E1-A988-DD39972A5E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="14220" activeTab="2" xr2:uid="{88DB3058-D681-4213-ADD3-9F3D01DF4147}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="14220" xr2:uid="{88DB3058-D681-4213-ADD3-9F3D01DF4147}"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -14,7 +19,6 @@
     <sheet name="contact" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="B1:E28"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,9 +45,6 @@
     <t>createorgtest</t>
   </si>
   <si>
-    <t>faceBook_</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -74,15 +75,9 @@
     <t>createorgTest</t>
   </si>
   <si>
-    <t>instagram_</t>
-  </si>
-  <si>
     <t>phoneNumber</t>
   </si>
   <si>
-    <t>8700507542</t>
-  </si>
-  <si>
     <t>createContactWithSupportDataTest</t>
   </si>
   <si>
@@ -195,6 +190,15 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>VerizonComm_</t>
+  </si>
+  <si>
+    <t>9550134378</t>
+  </si>
+  <si>
+    <t>SunPharma_</t>
   </si>
 </sst>
 </file>
@@ -606,7 +610,7 @@
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.4">
@@ -617,11 +621,11 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.4">
@@ -635,27 +639,27 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.4">
@@ -669,21 +673,21 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.4">
@@ -700,13 +704,13 @@
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -731,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.4">
@@ -745,13 +749,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -768,8 +772,8 @@
     <col min="2" max="2" width="55.90625" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="44.453125" customWidth="1"/>
-    <col min="5" max="5" width="17.90625" customWidth="1"/>
-    <col min="6" max="6" width="31.453125" customWidth="1"/>
+    <col min="5" max="5" width="37.7265625" customWidth="1"/>
+    <col min="6" max="6" width="83.6328125" customWidth="1"/>
     <col min="7" max="7" width="24.36328125" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
@@ -779,21 +783,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -801,33 +805,33 @@
         <v>0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.4">
@@ -835,51 +839,51 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -906,22 +910,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -934,22 +938,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -962,27 +966,27 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="E8" s="4"/>
     </row>
